--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0001T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0001T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.19865444640315</v>
+        <v>8.969781347540513</v>
       </c>
       <c r="D2" t="n">
-        <v>35.82672684879677</v>
+        <v>5.821843112929475</v>
       </c>
       <c r="E2" t="n">
-        <v>11.4181091887404</v>
+        <v>1.855442743170316</v>
       </c>
       <c r="F2" t="n">
-        <v>12.00337182106853</v>
+        <v>1.950547920923636</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.84824855065494</v>
+        <v>5.987840389481428</v>
       </c>
       <c r="D3" t="n">
-        <v>20.26681591075652</v>
+        <v>3.293357585497935</v>
       </c>
       <c r="E3" t="n">
-        <v>11.4181091887404</v>
+        <v>1.855442743170316</v>
       </c>
       <c r="F3" t="n">
-        <v>12.00337182106853</v>
+        <v>1.950547920923636</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>51.37698193807494</v>
+        <v>8.348759564937179</v>
       </c>
       <c r="D4" t="n">
-        <v>50.72433435567795</v>
+        <v>8.242704332797667</v>
       </c>
       <c r="E4" t="n">
-        <v>11.4181091887404</v>
+        <v>1.855442743170316</v>
       </c>
       <c r="F4" t="n">
-        <v>12.00337182106853</v>
+        <v>1.950547920923636</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>55.32679075764133</v>
+        <v>8.990603498116716</v>
       </c>
       <c r="D5" t="n">
-        <v>55.02020257590772</v>
+        <v>8.940782918585004</v>
       </c>
       <c r="E5" t="n">
-        <v>11.4181091887404</v>
+        <v>1.855442743170316</v>
       </c>
       <c r="F5" t="n">
-        <v>12.00337182106853</v>
+        <v>1.950547920923636</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>48.12942987593352</v>
+        <v>7.821032354839198</v>
       </c>
       <c r="D6" t="n">
-        <v>47.85192179523754</v>
+        <v>7.7759372917261</v>
       </c>
       <c r="E6" t="n">
-        <v>11.4181091887404</v>
+        <v>1.855442743170316</v>
       </c>
       <c r="F6" t="n">
-        <v>12.00337182106853</v>
+        <v>1.950547920923636</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.6300510623231</v>
+        <v>4.652383297627504</v>
       </c>
       <c r="D7" t="n">
-        <v>28.41772124335864</v>
+        <v>4.617879702045779</v>
       </c>
       <c r="E7" t="n">
-        <v>11.4181091887404</v>
+        <v>1.855442743170316</v>
       </c>
       <c r="F7" t="n">
-        <v>12.00337182106853</v>
+        <v>1.950547920923636</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.32584943310438</v>
+        <v>4.602950532879461</v>
       </c>
       <c r="D8" t="n">
-        <v>27.91975134189654</v>
+        <v>4.536959593058188</v>
       </c>
       <c r="E8" t="n">
-        <v>11.4181091887404</v>
+        <v>1.855442743170316</v>
       </c>
       <c r="F8" t="n">
-        <v>12.00337182106853</v>
+        <v>1.950547920923636</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>20.0333597706977</v>
+        <v>3.255420962738376</v>
       </c>
       <c r="D9" t="n">
-        <v>19.55190057350008</v>
+        <v>3.177183843193764</v>
       </c>
       <c r="E9" t="n">
-        <v>11.4181091887404</v>
+        <v>1.855442743170316</v>
       </c>
       <c r="F9" t="n">
-        <v>12.00337182106853</v>
+        <v>1.950547920923636</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>47.25409287007707</v>
+        <v>7.678790091387524</v>
       </c>
       <c r="D10" t="n">
-        <v>46.7719614277638</v>
+        <v>7.600443732011618</v>
       </c>
       <c r="E10" t="n">
-        <v>11.4181091887404</v>
+        <v>1.855442743170316</v>
       </c>
       <c r="F10" t="n">
-        <v>12.00337182106853</v>
+        <v>1.950547920923636</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>48.27466348916535</v>
+        <v>7.844632816989369</v>
       </c>
       <c r="D11" t="n">
-        <v>48.31274570621771</v>
+        <v>7.850821177260379</v>
       </c>
       <c r="E11" t="n">
-        <v>11.4181091887404</v>
+        <v>1.855442743170316</v>
       </c>
       <c r="F11" t="n">
-        <v>12.00337182106853</v>
+        <v>1.950547920923636</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>37.87137501140452</v>
+        <v>6.154098439353234</v>
       </c>
       <c r="D12" t="n">
-        <v>38.23298613676121</v>
+        <v>6.212860247223698</v>
       </c>
       <c r="E12" t="n">
-        <v>11.4181091887404</v>
+        <v>1.855442743170316</v>
       </c>
       <c r="F12" t="n">
-        <v>12.00337182106853</v>
+        <v>1.950547920923636</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
